--- a/exports/trend_1d/ADANIENSOL_full_report.xlsx
+++ b/exports/trend_1d/ADANIENSOL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>23.52</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H2" t="n">
-        <v>36.79</v>
+        <v>32.95</v>
       </c>
       <c r="I2" t="n">
         <v>34.38461</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.91</v>
+        <v>-17.52</v>
       </c>
       <c r="L2" t="n">
-        <v>13.77</v>
+        <v>19.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.98</v>
+        <v>4.87</v>
       </c>
       <c r="N2" t="n">
-        <v>5.37</v>
+        <v>10.44</v>
       </c>
       <c r="O2" t="n">
         <v>13.33</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>26.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42296</v>
+        <v>42297</v>
       </c>
       <c r="H3" t="n">
-        <v>29.05</v>
+        <v>34.85</v>
       </c>
       <c r="I3" t="n">
         <v>31.79494183103953</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>11.84</v>
+        <v>-5.77</v>
       </c>
       <c r="L3" t="n">
         <v>6.22</v>
@@ -612,7 +647,7 @@
         <v>3.19</v>
       </c>
       <c r="N3" t="n">
-        <v>6.78</v>
+        <v>19.97</v>
       </c>
       <c r="O3" t="n">
         <v>-10.44</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>25.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H4" t="n">
-        <v>34.35</v>
+        <v>31.95</v>
       </c>
       <c r="I4" t="n">
         <v>33.61012965539581</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.43</v>
+        <v>-8.32</v>
       </c>
       <c r="L4" t="n">
         <v>15.64</v>
@@ -669,7 +716,7 @@
         <v>3.93</v>
       </c>
       <c r="N4" t="n">
-        <v>5.85</v>
+        <v>6.99</v>
       </c>
       <c r="O4" t="n">
         <v>19.97</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>25.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42398</v>
+        <v>42401</v>
       </c>
       <c r="H5" t="n">
-        <v>36.75</v>
+        <v>39.1</v>
       </c>
       <c r="I5" t="n">
         <v>38.65123709307303</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.02</v>
+        <v>-22.38</v>
       </c>
       <c r="L5" t="n">
-        <v>16.43</v>
+        <v>23.47</v>
       </c>
       <c r="M5" t="n">
         <v>2.34</v>
       </c>
       <c r="N5" t="n">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
       <c r="O5" t="n">
         <v>-6.99</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>19.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H6" t="n">
-        <v>31.9</v>
+        <v>29.65</v>
       </c>
       <c r="I6" t="n">
         <v>31.45287547721816</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>-18.41</v>
+        <v>-24.17</v>
       </c>
       <c r="L6" t="n">
-        <v>20.2</v>
+        <v>25.19</v>
       </c>
       <c r="M6" t="n">
         <v>3.21</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>26.68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>33.95</v>
       </c>
       <c r="I7" t="n">
         <v>32.75077302446132</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.93</v>
+        <v>-14.5</v>
       </c>
       <c r="L7" t="n">
-        <v>10.29</v>
+        <v>17.54</v>
       </c>
       <c r="M7" t="n">
         <v>2.92</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>15.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42495</v>
+        <v>42496</v>
       </c>
       <c r="H8" t="n">
-        <v>30.55</v>
+        <v>30.15</v>
       </c>
       <c r="I8" t="n">
         <v>30.54976629463542</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.01</v>
+        <v>-11.19</v>
       </c>
       <c r="L8" t="n">
-        <v>10.75</v>
+        <v>11.93</v>
       </c>
       <c r="M8" t="n">
         <v>2.5</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>13.18</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42520</v>
+        <v>42521</v>
       </c>
       <c r="H9" t="n">
-        <v>31.3</v>
+        <v>31.9</v>
       </c>
       <c r="I9" t="n">
         <v>31.81535726652181</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.81</v>
+        <v>-5.8</v>
       </c>
       <c r="L9" t="n">
-        <v>7.13</v>
+        <v>7.46</v>
       </c>
       <c r="M9" t="n">
         <v>2.32</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H10" t="n">
-        <v>75.15000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>74.54455492838983</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>135.58</v>
+        <v>128.53</v>
       </c>
       <c r="L10" t="n">
         <v>3.61</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>227</v>
+        <v>228</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>20.39</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42866</v>
+        <v>42867</v>
       </c>
       <c r="H11" t="n">
-        <v>83.34999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>85.8754717977416</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>-14.33</v>
+        <v>-23.32</v>
       </c>
       <c r="L11" t="n">
-        <v>14.33</v>
+        <v>24.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0.73</v>
+        <v>1.32</v>
       </c>
       <c r="N11" t="n">
         <v>9.960000000000001</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>20.27</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H12" t="n">
-        <v>114.8</v>
+        <v>111.85</v>
       </c>
       <c r="I12" t="n">
         <v>113.51119972674</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>27.7</v>
+        <v>24.42</v>
       </c>
       <c r="L12" t="n">
         <v>8.51</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>21.63</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H13" t="n">
-        <v>117.7</v>
+        <v>124.5</v>
       </c>
       <c r="I13" t="n">
         <v>123.1847608141234</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.23</v>
+        <v>-11.31</v>
       </c>
       <c r="L13" t="n">
         <v>21.14</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.52</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H14" t="n">
-        <v>132.35</v>
+        <v>128.6</v>
       </c>
       <c r="I14" t="n">
         <v>128.8894979177324</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>6.31</v>
+        <v>3.29</v>
       </c>
       <c r="L14" t="n">
         <v>5.14</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>20.53</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43007</v>
+        <v>43011</v>
       </c>
       <c r="H15" t="n">
-        <v>152.8</v>
+        <v>158.6</v>
       </c>
       <c r="I15" t="n">
         <v>154.359974445553</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.82</v>
+        <v>-23.33</v>
       </c>
       <c r="L15" t="n">
-        <v>20.84</v>
+        <v>24.65</v>
       </c>
       <c r="M15" t="n">
         <v>3.73</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>17.98</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43042</v>
+        <v>43045</v>
       </c>
       <c r="H16" t="n">
-        <v>203.65</v>
+        <v>201.4</v>
       </c>
       <c r="I16" t="n">
         <v>201.6886693375551</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>28.4</v>
+        <v>26.99</v>
       </c>
       <c r="L16" t="n">
         <v>3.44</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>16.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H17" t="n">
-        <v>205.5</v>
+        <v>225.85</v>
       </c>
       <c r="I17" t="n">
         <v>205.8070293285695</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.04</v>
+        <v>-12.14</v>
       </c>
       <c r="L17" t="n">
-        <v>10.23</v>
+        <v>12.24</v>
       </c>
       <c r="M17" t="n">
         <v>4.03</v>
       </c>
       <c r="N17" t="n">
-        <v>5.83</v>
+        <v>9.9</v>
       </c>
       <c r="O17" t="n">
         <v>-1.1</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>20.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H18" t="n">
-        <v>207.3</v>
+        <v>193.8</v>
       </c>
       <c r="I18" t="n">
         <v>202.0914419831375</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.210000000000001</v>
+        <v>-14.19</v>
       </c>
       <c r="L18" t="n">
-        <v>9.869999999999999</v>
+        <v>16.71</v>
       </c>
       <c r="M18" t="n">
         <v>1.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4.19</v>
+        <v>6.51</v>
       </c>
       <c r="O18" t="n">
         <v>9.9</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>19.43</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43265</v>
+        <v>43266</v>
       </c>
       <c r="H19" t="n">
-        <v>144.8</v>
+        <v>149.15</v>
       </c>
       <c r="I19" t="n">
         <v>149.0545329376865</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K19" t="n">
-        <v>25.28</v>
+        <v>23.04</v>
       </c>
       <c r="L19" t="n">
         <v>13</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>17.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H20" t="n">
-        <v>197.15</v>
+        <v>191.65</v>
       </c>
       <c r="I20" t="n">
         <v>192.9630599453136</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K20" t="n">
-        <v>32.18</v>
+        <v>28.49</v>
       </c>
       <c r="L20" t="n">
         <v>4.36</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>21.91</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H21" t="n">
-        <v>166.45</v>
+        <v>176.6</v>
       </c>
       <c r="I21" t="n">
         <v>174.4871431127518</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K21" t="n">
-        <v>13.15</v>
+        <v>7.85</v>
       </c>
       <c r="L21" t="n">
         <v>4.57</v>
@@ -1638,7 +1889,7 @@
         <v>4.63</v>
       </c>
       <c r="N21" t="n">
-        <v>4.98</v>
+        <v>6.1</v>
       </c>
       <c r="O21" t="n">
         <v>-2.79</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>16.7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43455</v>
+        <v>43458</v>
       </c>
       <c r="H22" t="n">
-        <v>208.35</v>
+        <v>200.05</v>
       </c>
       <c r="I22" t="n">
         <v>205.5119686360962</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K22" t="n">
-        <v>17.98</v>
+        <v>13.28</v>
       </c>
       <c r="L22" t="n">
         <v>5.86</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>17.21</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43475</v>
+        <v>43476</v>
       </c>
       <c r="H23" t="n">
-        <v>215.85</v>
+        <v>221.4</v>
       </c>
       <c r="I23" t="n">
         <v>221.0329267276298</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.9</v>
+        <v>-10.67</v>
       </c>
       <c r="L23" t="n">
-        <v>9.220000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.5</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43521</v>
+        <v>43522</v>
       </c>
       <c r="H24" t="n">
-        <v>210.3</v>
+        <v>196.2</v>
       </c>
       <c r="I24" t="n">
         <v>197.5957057518805</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.01</v>
+        <v>-11.38</v>
       </c>
       <c r="L24" t="n">
-        <v>11.43</v>
+        <v>13.53</v>
       </c>
       <c r="M24" t="n">
         <v>1.73</v>
       </c>
       <c r="N24" t="n">
-        <v>3.71</v>
+        <v>6.7</v>
       </c>
       <c r="O24" t="n">
         <v>2.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>16.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43538</v>
+        <v>43539</v>
       </c>
       <c r="H25" t="n">
-        <v>206.6</v>
+        <v>235.2</v>
       </c>
       <c r="I25" t="n">
         <v>224.5842252395149</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.3</v>
+        <v>-19.88</v>
       </c>
       <c r="L25" t="n">
-        <v>11.93</v>
+        <v>24.52</v>
       </c>
       <c r="M25" t="n">
         <v>2.07</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>13.84</v>
       </c>
       <c r="O25" t="n">
         <v>-6.7</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>18.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43675</v>
+        <v>43676</v>
       </c>
       <c r="H26" t="n">
-        <v>207.8</v>
+        <v>203.95</v>
       </c>
       <c r="I26" t="n">
         <v>206.5788593976508</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.65</v>
+        <v>-13.29</v>
       </c>
       <c r="L26" t="n">
         <v>13.99</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>14.21</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H27" t="n">
-        <v>229.1</v>
+        <v>236.3</v>
       </c>
       <c r="I27" t="n">
         <v>230.3154051942593</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>-12.33</v>
+        <v>-15.86</v>
       </c>
       <c r="L27" t="n">
-        <v>13.7</v>
+        <v>18.17</v>
       </c>
       <c r="M27" t="n">
         <v>2.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43878</v>
+        <v>43879</v>
       </c>
       <c r="H28" t="n">
-        <v>314.65</v>
+        <v>301.2</v>
       </c>
       <c r="I28" t="n">
         <v>309.7830569701721</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K28" t="n">
-        <v>33.16</v>
+        <v>27.47</v>
       </c>
       <c r="L28" t="n">
         <v>8.93</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>15.25</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43994</v>
+        <v>43997</v>
       </c>
       <c r="H29" t="n">
-        <v>202.75</v>
+        <v>209.75</v>
       </c>
       <c r="I29" t="n">
         <v>203.5057919265096</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K29" t="n">
-        <v>32.69</v>
+        <v>30.36</v>
       </c>
       <c r="L29" t="n">
         <v>10.23</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.28</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44035</v>
+        <v>44036</v>
       </c>
       <c r="H30" t="n">
-        <v>239.55</v>
+        <v>233.05</v>
       </c>
       <c r="I30" t="n">
         <v>234.0042771889077</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
-        <v>14.21</v>
+        <v>11.11</v>
       </c>
       <c r="L30" t="n">
         <v>4.24</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>12.95</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44062</v>
+        <v>44063</v>
       </c>
       <c r="H31" t="n">
-        <v>245.15</v>
+        <v>269.65</v>
       </c>
       <c r="I31" t="n">
         <v>257.9449206597789</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.19</v>
+        <v>-15.7</v>
       </c>
       <c r="L31" t="n">
-        <v>12.4</v>
+        <v>15.7</v>
       </c>
       <c r="M31" t="n">
         <v>2.1</v>
       </c>
       <c r="N31" t="n">
-        <v>8.050000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="O31" t="n">
         <v>-2.71</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44096</v>
+        <v>44097</v>
       </c>
       <c r="H32" t="n">
-        <v>246.7</v>
+        <v>241.75</v>
       </c>
       <c r="I32" t="n">
         <v>244.4518178974336</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.51</v>
+        <v>-10.35</v>
       </c>
       <c r="L32" t="n">
         <v>14.09</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>18.03</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H33" t="n">
-        <v>272.05</v>
+        <v>281.6</v>
       </c>
       <c r="I33" t="n">
         <v>277.5266296562501</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>-12.53</v>
+        <v>-16.48</v>
       </c>
       <c r="L33" t="n">
-        <v>13.67</v>
+        <v>17.48</v>
       </c>
       <c r="M33" t="n">
         <v>1.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.27</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H34" t="n">
-        <v>432.85</v>
+        <v>406.1</v>
       </c>
       <c r="I34" t="n">
         <v>408.0830734269611</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K34" t="n">
-        <v>53.71</v>
+        <v>44.21</v>
       </c>
       <c r="L34" t="n">
         <v>2.52</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>16.11</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H35" t="n">
-        <v>455.2</v>
+        <v>471.65</v>
       </c>
       <c r="I35" t="n">
         <v>470.5285722324121</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-12.09</v>
+        <v>-16.14</v>
       </c>
       <c r="L35" t="n">
-        <v>12.78</v>
+        <v>17.7</v>
       </c>
       <c r="M35" t="n">
         <v>0.96</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.61</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H36" t="n">
-        <v>973.55</v>
+        <v>924.9</v>
       </c>
       <c r="I36" t="n">
         <v>942.1034802886719</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K36" t="n">
-        <v>106.41</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>5.01</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>21.22</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44320</v>
+        <v>44321</v>
       </c>
       <c r="H37" t="n">
-        <v>1065.35</v>
+        <v>1088.2</v>
       </c>
       <c r="I37" t="n">
         <v>1075.771443924342</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>-15.19</v>
+        <v>-17.66</v>
       </c>
       <c r="L37" t="n">
-        <v>18.39</v>
+        <v>19.47</v>
       </c>
       <c r="M37" t="n">
         <v>2.25</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44362</v>
+        <v>44363</v>
       </c>
       <c r="H38" t="n">
-        <v>1446.4</v>
+        <v>1374.1</v>
       </c>
       <c r="I38" t="n">
         <v>1401.101958603498</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>32.92</v>
+        <v>26.27</v>
       </c>
       <c r="L38" t="n">
         <v>2.06</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44425</v>
+        <v>44426</v>
       </c>
       <c r="H39" t="n">
-        <v>1024</v>
+        <v>1075.2</v>
       </c>
       <c r="I39" t="n">
         <v>1070.432410774662</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K39" t="n">
-        <v>25.48</v>
+        <v>21.75</v>
       </c>
       <c r="L39" t="n">
         <v>2.54</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>17.57</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44459</v>
+        <v>44460</v>
       </c>
       <c r="H40" t="n">
-        <v>1729.35</v>
+        <v>1642.9</v>
       </c>
       <c r="I40" t="n">
         <v>1692.841552823338</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>60.84</v>
+        <v>52.8</v>
       </c>
       <c r="L40" t="n">
         <v>6.06</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>16.51</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H41" t="n">
-        <v>1789.6</v>
+        <v>1809</v>
       </c>
       <c r="I41" t="n">
         <v>1796.478616558392</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.93</v>
+        <v>-10.11</v>
       </c>
       <c r="L41" t="n">
-        <v>9.5</v>
+        <v>11.21</v>
       </c>
       <c r="M41" t="n">
         <v>2.37</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>15.25</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44559</v>
+        <v>44560</v>
       </c>
       <c r="H42" t="n">
-        <v>1727.8</v>
+        <v>1683.4</v>
       </c>
       <c r="I42" t="n">
         <v>1694.312044733122</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.49</v>
+        <v>-6.94</v>
       </c>
       <c r="L42" t="n">
-        <v>6.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>5</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>13.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H43" t="n">
-        <v>1867.45</v>
+        <v>1928.25</v>
       </c>
       <c r="I43" t="n">
         <v>1913.08944170777</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" t="n">
-        <v>-10.93</v>
+        <v>-14.54</v>
       </c>
       <c r="L43" t="n">
-        <v>12.21</v>
+        <v>16.31</v>
       </c>
       <c r="M43" t="n">
         <v>1.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.84</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H44" t="n">
-        <v>2482.55</v>
+        <v>2296</v>
       </c>
       <c r="I44" t="n">
         <v>2324.01371824568</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K44" t="n">
-        <v>28.75</v>
+        <v>19.07</v>
       </c>
       <c r="L44" t="n">
         <v>6.13</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>32.84</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44741</v>
+        <v>44742</v>
       </c>
       <c r="H45" t="n">
-        <v>2347.9</v>
+        <v>2473.65</v>
       </c>
       <c r="I45" t="n">
         <v>2385.165200233051</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.26</v>
+        <v>-7.74</v>
       </c>
       <c r="L45" t="n">
         <v>15.41</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>16.61</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H46" t="n">
-        <v>3713</v>
+        <v>3606.5</v>
       </c>
       <c r="I46" t="n">
         <v>3651.223191622115</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K46" t="n">
-        <v>50.1</v>
+        <v>45.8</v>
       </c>
       <c r="L46" t="n">
         <v>10</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>17.79</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44944</v>
+        <v>44945</v>
       </c>
       <c r="H47" t="n">
-        <v>2710.75</v>
+        <v>2734.1</v>
       </c>
       <c r="I47" t="n">
         <v>2728.359012915157</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K47" t="n">
-        <v>24.84</v>
+        <v>24.19</v>
       </c>
       <c r="L47" t="n">
         <v>5.23</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>13.52</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H48" t="n">
-        <v>2517.75</v>
+        <v>2014.2</v>
       </c>
       <c r="I48" t="n">
         <v>2467.07623735465</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.91</v>
+        <v>-26.33</v>
       </c>
       <c r="L48" t="n">
-        <v>10.98</v>
+        <v>26.33</v>
       </c>
       <c r="M48" t="n">
-        <v>1.53</v>
+        <v>4.44</v>
       </c>
       <c r="N48" t="n">
-        <v>8.85</v>
+        <v>20</v>
       </c>
       <c r="O48" t="n">
         <v>0.86</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>34.59</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44994</v>
+        <v>44995</v>
       </c>
       <c r="H49" t="n">
-        <v>861.4</v>
+        <v>904.45</v>
       </c>
       <c r="I49" t="n">
         <v>870.4111627902868</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>57.23</v>
+        <v>55.1</v>
       </c>
       <c r="L49" t="n">
         <v>21.54</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>21.06</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H50" t="n">
-        <v>943.4</v>
+        <v>907.85</v>
       </c>
       <c r="I50" t="n">
         <v>915.0088741589416</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K50" t="n">
-        <v>4.31</v>
+        <v>0.38</v>
       </c>
       <c r="L50" t="n">
         <v>5.24</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>23.77</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="H51" t="n">
-        <v>868</v>
+        <v>911.4</v>
       </c>
       <c r="I51" t="n">
         <v>897.3447812391721</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K51" t="n">
-        <v>4.39</v>
+        <v>-0.39</v>
       </c>
       <c r="L51" t="n">
         <v>21.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>16.94</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H52" t="n">
-        <v>804.4</v>
+        <v>757.5</v>
       </c>
       <c r="I52" t="n">
         <v>759.3571040289792</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.74</v>
+        <v>-16.89</v>
       </c>
       <c r="L52" t="n">
-        <v>15.76</v>
+        <v>19.03</v>
       </c>
       <c r="M52" t="n">
         <v>3.29</v>
       </c>
       <c r="N52" t="n">
-        <v>4.67</v>
+        <v>5.83</v>
       </c>
       <c r="O52" t="n">
         <v>5</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>14.3</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H53" t="n">
-        <v>773.25</v>
+        <v>834.85</v>
       </c>
       <c r="I53" t="n">
         <v>812.4716825848288</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.08</v>
+        <v>-10.21</v>
       </c>
       <c r="L53" t="n">
-        <v>9.4</v>
+        <v>11.29</v>
       </c>
       <c r="M53" t="n">
         <v>1.92</v>
       </c>
       <c r="N53" t="n">
-        <v>5.94</v>
+        <v>7.97</v>
       </c>
       <c r="O53" t="n">
         <v>-5.83</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>12.6</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H54" t="n">
-        <v>857.15</v>
+        <v>841.7</v>
       </c>
       <c r="I54" t="n">
         <v>843.0115135565989</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>2.67</v>
+        <v>0.82</v>
       </c>
       <c r="L54" t="n">
         <v>7.7</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>15.02</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45254</v>
+        <v>45258</v>
       </c>
       <c r="H55" t="n">
-        <v>729.1</v>
+        <v>865.1</v>
       </c>
       <c r="I55" t="n">
         <v>778.2946543163729</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K55" t="n">
-        <v>13.38</v>
+        <v>-2.78</v>
       </c>
       <c r="L55" t="n">
         <v>5.59</v>
@@ -3576,7 +4235,7 @@
         <v>3.28</v>
       </c>
       <c r="N55" t="n">
-        <v>5.22</v>
+        <v>18.65</v>
       </c>
       <c r="O55" t="n">
         <v>-1.8</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>16.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H56" t="n">
-        <v>1037.25</v>
+        <v>947.95</v>
       </c>
       <c r="I56" t="n">
         <v>1012.098128047883</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K56" t="n">
-        <v>19.9</v>
+        <v>9.58</v>
       </c>
       <c r="L56" t="n">
         <v>13.77</v>
@@ -3633,7 +4304,7 @@
         <v>1.7</v>
       </c>
       <c r="N56" t="n">
-        <v>7.18</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O56" t="n">
         <v>18.65</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>17.82</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H57" t="n">
-        <v>1061.4</v>
+        <v>1086.95</v>
       </c>
       <c r="I57" t="n">
         <v>1081.285873401594</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.97</v>
+        <v>-14.66</v>
       </c>
       <c r="L57" t="n">
         <v>19.08</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>10.03</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H58" t="n">
-        <v>1221.95</v>
+        <v>977.6</v>
       </c>
       <c r="I58" t="n">
         <v>1079.000754154627</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>12.42</v>
+        <v>-10.06</v>
       </c>
       <c r="L58" t="n">
-        <v>2.24</v>
+        <v>10.06</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="N58" t="n">
-        <v>1.47</v>
+        <v>20</v>
       </c>
       <c r="O58" t="n">
         <v>2.41</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>32.61</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45502</v>
+        <v>45503</v>
       </c>
       <c r="H59" t="n">
-        <v>1051.95</v>
+        <v>1124.9</v>
       </c>
       <c r="I59" t="n">
         <v>1079.475259234458</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.61</v>
+        <v>-15.07</v>
       </c>
       <c r="L59" t="n">
         <v>24.77</v>
@@ -3804,7 +4511,7 @@
         <v>4.55</v>
       </c>
       <c r="N59" t="n">
-        <v>5.19</v>
+        <v>6.93</v>
       </c>
       <c r="O59" t="n">
         <v>-20</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>14.58</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45513</v>
+        <v>45516</v>
       </c>
       <c r="H60" t="n">
-        <v>1103.8</v>
+        <v>1063</v>
       </c>
       <c r="I60" t="n">
         <v>1076.281390879484</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.88</v>
+        <v>-5.5</v>
       </c>
       <c r="L60" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="M60" t="n">
         <v>4.9</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>17.37</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H61" t="n">
-        <v>1015</v>
+        <v>1076.3</v>
       </c>
       <c r="I61" t="n">
         <v>1060.727687108355</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K61" t="n">
-        <v>4.52</v>
+        <v>-1.25</v>
       </c>
       <c r="L61" t="n">
         <v>7.06</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>15.18</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="H62" t="n">
-        <v>936.25</v>
+        <v>901.95</v>
       </c>
       <c r="I62" t="n">
         <v>912.8799579669035</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>-13.01</v>
+        <v>-16.2</v>
       </c>
       <c r="L62" t="n">
-        <v>13.22</v>
+        <v>16.66</v>
       </c>
       <c r="M62" t="n">
         <v>6.51</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>18.51</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H63" t="n">
-        <v>726.85</v>
+        <v>840.5</v>
       </c>
       <c r="I63" t="n">
         <v>790.0392712364212</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K63" t="n">
-        <v>19.41</v>
+        <v>6.81</v>
       </c>
       <c r="L63" t="n">
         <v>3.99</v>
@@ -4032,7 +4787,7 @@
         <v>4.48</v>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>15.64</v>
       </c>
       <c r="O63" t="n">
         <v>-3.66</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>28.59</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H64" t="n">
-        <v>751.5</v>
+        <v>729.25</v>
       </c>
       <c r="I64" t="n">
         <v>733.3065930382373</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K64" t="n">
-        <v>-10.59</v>
+        <v>-13.24</v>
       </c>
       <c r="L64" t="n">
-        <v>11.72</v>
+        <v>13.58</v>
       </c>
       <c r="M64" t="n">
         <v>2.37</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>13.78</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H65" t="n">
-        <v>792.5</v>
+        <v>805.15</v>
       </c>
       <c r="I65" t="n">
         <v>797.7799244391662</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-8.67</v>
+        <v>-10.41</v>
       </c>
       <c r="L65" t="n">
         <v>14.25</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>14.86</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H66" t="n">
-        <v>744</v>
+        <v>708.4</v>
       </c>
       <c r="I66" t="n">
         <v>709.8840830011251</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="n">
-        <v>-7.59</v>
+        <v>-12.02</v>
       </c>
       <c r="L66" t="n">
-        <v>9.93</v>
+        <v>13.46</v>
       </c>
       <c r="M66" t="n">
         <v>1.42</v>
       </c>
       <c r="N66" t="n">
-        <v>4.4</v>
+        <v>4.78</v>
       </c>
       <c r="O66" t="n">
         <v>1.6</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>16.73</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H67" t="n">
-        <v>709.45</v>
+        <v>733.25</v>
       </c>
       <c r="I67" t="n">
         <v>732.8064055683451</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.15</v>
+        <v>-3.51</v>
       </c>
       <c r="L67" t="n">
         <v>6.03</v>
       </c>
       <c r="M67" t="n">
-        <v>0.68</v>
+        <v>1.35</v>
       </c>
       <c r="N67" t="n">
         <v>9.710000000000001</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>14.63</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H68" t="n">
-        <v>871.6</v>
+        <v>839</v>
       </c>
       <c r="I68" t="n">
         <v>848.212332148515</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K68" t="n">
-        <v>18.87</v>
+        <v>14.42</v>
       </c>
       <c r="L68" t="n">
         <v>3.5</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>17.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H69" t="n">
-        <v>794.15</v>
+        <v>811.75</v>
       </c>
       <c r="I69" t="n">
         <v>805.2698718775928</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K69" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="L69" t="n">
         <v>11.41</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.9</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H70" t="n">
-        <v>994.3</v>
+        <v>960.6</v>
       </c>
       <c r="I70" t="n">
         <v>984.5800637483472</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K70" t="n">
-        <v>22.49</v>
+        <v>18.34</v>
       </c>
       <c r="L70" t="n">
         <v>2.43</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>10.21</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H71" t="n">
-        <v>884.6</v>
+        <v>974.4</v>
       </c>
       <c r="I71" t="n">
         <v>953.8273705494737</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>7.91</v>
+        <v>-1.44</v>
       </c>
       <c r="L71" t="n">
         <v>4.01</v>
       </c>
       <c r="M71" t="n">
-        <v>2.13</v>
+        <v>7.51</v>
       </c>
       <c r="N71" t="n">
-        <v>4.59</v>
+        <v>10.15</v>
       </c>
       <c r="O71" t="n">
         <v>-3.39</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>16.62</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H72" t="n">
-        <v>1603</v>
+        <v>1540.7</v>
       </c>
       <c r="I72" t="n">
         <v>1578.508527180707</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K72" t="n">
-        <v>64.51000000000001</v>
+        <v>58.12</v>
       </c>
       <c r="L72" t="n">
         <v>7.31</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>7</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>48</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9359,7 +10242,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.2</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="6">
@@ -9369,7 +10252,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -9379,7 +10262,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8">
@@ -9389,7 +10272,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9399,7 +10282,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -9409,7 +10292,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -9419,7 +10302,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -9429,7 +10312,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -9439,7 +10322,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.4</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="14">
@@ -9449,7 +10332,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.859999999999999</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="15">
@@ -9459,7 +10342,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.92</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -9469,7 +10352,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.58</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="17">
@@ -9479,7 +10362,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>135.58</v>
+        <v>128.53</v>
       </c>
     </row>
     <row r="18">
@@ -9489,7 +10372,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.9</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="19">
@@ -9499,7 +10382,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.17</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="20">
@@ -9509,7 +10392,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.93</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="21">
@@ -9519,7 +10402,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.77</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="22">
@@ -9529,7 +10412,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -9539,7 +10422,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -9549,7 +10432,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="25">
@@ -9569,7 +10452,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.45</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="27">
@@ -9579,7 +10462,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -9589,7 +10472,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
